--- a/data/trans_dic/P59A-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P59A-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que vive actualmente en pareja</t>
+          <t>Población que vive actualmente en pareja (tasa de respuesta: 98,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,12; 11,05</t>
+          <t>5,12; 11,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,29; 15,4</t>
+          <t>8,05; 15,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,18; 13,52</t>
+          <t>6,16; 13,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,5; 15,57</t>
+          <t>6,58; 15,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,04; 7,01</t>
+          <t>3,18; 7,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,81; 9,88</t>
+          <t>4,8; 9,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,99; 9,26</t>
+          <t>3,86; 8,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,76; 8,26</t>
+          <t>3,81; 8,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,3; 7,71</t>
+          <t>4,45; 7,73</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,58; 10,93</t>
+          <t>6,84; 10,75</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,3; 9,43</t>
+          <t>5,33; 9,22</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,24; 9,52</t>
+          <t>5,29; 9,53</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,86; 17,5</t>
+          <t>12,06; 17,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,37; 18,59</t>
+          <t>13,17; 18,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,41; 21,6</t>
+          <t>15,93; 21,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,25; 19,4</t>
+          <t>13,55; 19,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,71; 14,84</t>
+          <t>9,6; 14,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,4; 20,15</t>
+          <t>14,57; 20,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,44; 19,36</t>
+          <t>14,58; 19,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,6; 16,39</t>
+          <t>10,81; 16,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,65; 15,26</t>
+          <t>11,62; 15,39</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14,48; 18,42</t>
+          <t>14,6; 18,56</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,18; 19,65</t>
+          <t>15,95; 19,61</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,1; 17,23</t>
+          <t>13,13; 17,11</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,26; 24,26</t>
+          <t>14,73; 24,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,83; 25,99</t>
+          <t>13,96; 25,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,42; 27,51</t>
+          <t>16,2; 27,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,56; 24,83</t>
+          <t>14,33; 24,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,61; 22,91</t>
+          <t>12,58; 22,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,58; 29,09</t>
+          <t>15,47; 28,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,08; 22,5</t>
+          <t>13,25; 22,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,27; 24,54</t>
+          <t>16,46; 24,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,75; 22,31</t>
+          <t>14,8; 22,41</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,49; 25,33</t>
+          <t>16,45; 25,15</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16,49; 24,07</t>
+          <t>16,23; 23,63</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,24; 22,87</t>
+          <t>16,2; 22,97</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,76; 15,88</t>
+          <t>11,83; 15,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,61; 17,57</t>
+          <t>13,44; 17,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,36; 19,63</t>
+          <t>15,41; 19,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,76; 18,43</t>
+          <t>13,71; 18,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,6; 11,87</t>
+          <t>8,57; 12,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,5; 16,49</t>
+          <t>12,45; 16,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,58; 15,92</t>
+          <t>12,36; 15,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,33; 15,1</t>
+          <t>11,19; 14,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,55; 13,19</t>
+          <t>10,65; 13,25</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13,36; 16,32</t>
+          <t>13,37; 16,24</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,39; 17,17</t>
+          <t>14,37; 17,08</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,95; 15,91</t>
+          <t>12,92; 15,83</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que vive actualmente en pareja</t>
+          <t>Población que vive actualmente en pareja (tasa de respuesta: 98,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>15842; 34179</t>
+          <t>15852; 34724</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>25242; 46895</t>
+          <t>24519; 46723</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16437; 35932</t>
+          <t>16380; 35311</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14970; 35843</t>
+          <t>15146; 35713</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15339; 35379</t>
+          <t>16065; 35416</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23787; 48848</t>
+          <t>23727; 47936</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16211; 37567</t>
+          <t>15652; 36155</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15435; 33932</t>
+          <t>15673; 34811</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>34999; 62732</t>
+          <t>36207; 62938</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>52550; 87266</t>
+          <t>54654; 85882</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35604; 63331</t>
+          <t>35777; 61953</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>33569; 61064</t>
+          <t>33940; 61071</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>88764; 130919</t>
+          <t>90208; 129305</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>115120; 160122</t>
+          <t>113411; 159934</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>153807; 202550</t>
+          <t>149311; 198152</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>146245; 214089</t>
+          <t>149551; 214511</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>63439; 96962</t>
+          <t>62750; 97435</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>104813; 146711</t>
+          <t>106073; 149002</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>132801; 178024</t>
+          <t>134115; 177185</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>106584; 164853</t>
+          <t>108722; 166553</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>163322; 213908</t>
+          <t>162887; 215696</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>230061; 292717</t>
+          <t>232061; 294979</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>300411; 364837</t>
+          <t>296197; 364180</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>276334; 363533</t>
+          <t>276940; 360972</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>32866; 55940</t>
+          <t>33955; 57371</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>29565; 55570</t>
+          <t>29846; 55352</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40812; 68349</t>
+          <t>40262; 67385</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39590; 72511</t>
+          <t>41845; 71731</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>28284; 51364</t>
+          <t>28203; 51163</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30771; 57432</t>
+          <t>30543; 55595</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33918; 58342</t>
+          <t>34352; 59391</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>53952; 81368</t>
+          <t>54572; 82073</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>67089; 101454</t>
+          <t>67313; 101901</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>67817; 104174</t>
+          <t>67637; 103445</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>83747; 122248</t>
+          <t>82388; 119993</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>101292; 142632</t>
+          <t>101040; 143252</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>151556; 204574</t>
+          <t>152374; 203455</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>187770; 242377</t>
+          <t>185434; 240801</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>223046; 285012</t>
+          <t>223686; 283670</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>223729; 299709</t>
+          <t>222946; 298835</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>118904; 164076</t>
+          <t>118514; 167653</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>177407; 234163</t>
+          <t>176761; 233170</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>199292; 252336</t>
+          <t>195943; 249785</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>198021; 263968</t>
+          <t>195638; 260499</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>281649; 352236</t>
+          <t>284463; 353780</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>373897; 456866</t>
+          <t>374383; 454747</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>437005; 521440</t>
+          <t>436242; 518646</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>437024; 536880</t>
+          <t>435763; 534167</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P59A-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P59A-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,12; 11,22</t>
+          <t>5,06; 11,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,05; 15,34</t>
+          <t>8,15; 15,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,16; 13,29</t>
+          <t>6,07; 13,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,58; 15,52</t>
+          <t>5,48; 14,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,18; 7,02</t>
+          <t>2,88; 6,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,8; 9,7</t>
+          <t>4,79; 9,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,86; 8,91</t>
+          <t>3,93; 8,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,81; 8,47</t>
+          <t>3,58; 7,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,45; 7,73</t>
+          <t>4,36; 7,8</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,84; 10,75</t>
+          <t>6,83; 10,66</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,33; 9,22</t>
+          <t>5,22; 9,26</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,29; 9,53</t>
+          <t>4,98; 9,09</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>16,15%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,06; 17,28</t>
+          <t>11,89; 17,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,17; 18,57</t>
+          <t>13,08; 18,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,93; 21,14</t>
+          <t>16,02; 21,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,55; 19,44</t>
+          <t>14,52; 20,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,6; 14,91</t>
+          <t>9,6; 14,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,57; 20,47</t>
+          <t>14,79; 20,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,58; 19,27</t>
+          <t>14,41; 19,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,81; 16,56</t>
+          <t>12,8; 17,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,62; 15,39</t>
+          <t>11,4; 15,25</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14,6; 18,56</t>
+          <t>14,39; 18,38</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,95; 19,61</t>
+          <t>16,07; 19,65</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,13; 17,11</t>
+          <t>14,41; 18,03</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,8%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,73; 24,88</t>
+          <t>14,13; 25,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,96; 25,89</t>
+          <t>14,19; 25,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,2; 27,12</t>
+          <t>16,95; 27,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,33; 24,56</t>
+          <t>14,87; 24,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,58; 22,82</t>
+          <t>12,83; 23,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,47; 28,16</t>
+          <t>15,99; 28,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,25; 22,91</t>
+          <t>13,21; 22,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,46; 24,75</t>
+          <t>16,4; 24,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,8; 22,41</t>
+          <t>14,71; 22,15</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,45; 25,15</t>
+          <t>16,45; 25,0</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16,23; 23,63</t>
+          <t>15,84; 23,3</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,2; 22,97</t>
+          <t>16,72; 22,9</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>15,04%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,83; 15,79</t>
+          <t>11,82; 15,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,44; 17,45</t>
+          <t>13,48; 17,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,41; 19,54</t>
+          <t>15,48; 19,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,71; 18,38</t>
+          <t>14,19; 18,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,57; 12,13</t>
+          <t>8,62; 12,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,45; 16,42</t>
+          <t>12,4; 16,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,36; 15,76</t>
+          <t>12,65; 16,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,19; 14,9</t>
+          <t>12,38; 15,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,65; 13,25</t>
+          <t>10,65; 13,38</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13,37; 16,24</t>
+          <t>13,47; 16,24</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,37; 17,08</t>
+          <t>14,46; 17,04</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,92; 15,83</t>
+          <t>13,7; 16,33</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23190</t>
+          <t>24687</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>23172</t>
+          <t>23156</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>46361</t>
+          <t>47843</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>15852; 34724</t>
+          <t>15666; 35331</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>24519; 46723</t>
+          <t>24814; 46878</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16380; 35311</t>
+          <t>16120; 35048</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15146; 35713</t>
+          <t>14083; 37123</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>16065; 35416</t>
+          <t>14523; 35187</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23727; 47936</t>
+          <t>23667; 47702</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15652; 36155</t>
+          <t>15943; 35174</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15673; 34811</t>
+          <t>15831; 34002</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>36207; 62938</t>
+          <t>35524; 63532</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>54654; 85882</t>
+          <t>54526; 85135</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35777; 61953</t>
+          <t>35051; 62223</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>33940; 61071</t>
+          <t>34806; 63517</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>180144</t>
+          <t>200066</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>138938</t>
+          <t>160788</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>319082</t>
+          <t>360854</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>90208; 129305</t>
+          <t>88983; 128484</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>113411; 159934</t>
+          <t>112672; 159763</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>149311; 198152</t>
+          <t>150207; 201684</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>149551; 214511</t>
+          <t>170169; 236126</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>62750; 97435</t>
+          <t>62758; 95441</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>106073; 149002</t>
+          <t>107705; 147552</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>134115; 177185</t>
+          <t>132516; 176836</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>108722; 166553</t>
+          <t>135906; 184737</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>162887; 215696</t>
+          <t>159779; 213690</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>232061; 294979</t>
+          <t>228737; 292175</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>296197; 364180</t>
+          <t>298520; 364915</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>276940; 360972</t>
+          <t>322021; 402775</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55172</t>
+          <t>60445</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>66889</t>
+          <t>73743</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>122060</t>
+          <t>134188</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>33955; 57371</t>
+          <t>32566; 58540</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>29846; 55352</t>
+          <t>30350; 55112</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40262; 67385</t>
+          <t>42114; 68567</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41845; 71731</t>
+          <t>46709; 77897</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>28203; 51163</t>
+          <t>28757; 52632</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30543; 55595</t>
+          <t>31582; 56600</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34352; 59391</t>
+          <t>34263; 58622</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>54572; 82073</t>
+          <t>59593; 88504</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>67313; 101901</t>
+          <t>66880; 100745</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>67637; 103445</t>
+          <t>67651; 102799</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>82388; 119993</t>
+          <t>80413; 118304</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>101040; 143252</t>
+          <t>113325; 155188</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>258506</t>
+          <t>285198</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>228998</t>
+          <t>257687</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>487504</t>
+          <t>542885</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>152374; 203455</t>
+          <t>152328; 203813</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>185434; 240801</t>
+          <t>186033; 241360</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>223686; 283670</t>
+          <t>224680; 284586</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>222946; 298835</t>
+          <t>247448; 324797</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>118514; 167653</t>
+          <t>119166; 166694</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>176761; 233170</t>
+          <t>176003; 232477</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>195943; 249785</t>
+          <t>200525; 254476</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>195638; 260499</t>
+          <t>231172; 289584</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>284463; 353780</t>
+          <t>284529; 357341</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>374383; 454747</t>
+          <t>377113; 454723</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>436242; 518646</t>
+          <t>439203; 517434</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>435763; 534167</t>
+          <t>494763; 589512</t>
         </is>
       </c>
     </row>
